--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487546_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487546_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.4414</v>
+        <v>11.9579</v>
       </c>
       <c r="E2" t="n">
-        <v>8.6829</v>
+        <v>9.065799999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7585</v>
+        <v>2.8921</v>
       </c>
       <c r="G2" t="n">
         <v>9.381399999999999</v>
@@ -610,13 +610,13 @@
         <v>3.5253</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0683</v>
+        <v>-0.5518</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7258</v>
+        <v>-0.3429</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3426</v>
+        <v>-0.2089</v>
       </c>
       <c r="V2" t="n">
         <v>-0.397</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2523</v>
+        <v>4.3712</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2938</v>
+        <v>3.6533</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9585</v>
+        <v>0.7179</v>
       </c>
       <c r="G3" t="n">
         <v>1.6167</v>
@@ -688,13 +688,13 @@
         <v>3.7211</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6824</v>
+        <v>-0.1986</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5199</v>
+        <v>-0.1206</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1625</v>
+        <v>-0.0781</v>
       </c>
       <c r="V3" t="n">
         <v>0.2113</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2275</v>
+        <v>4.2824</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9307</v>
+        <v>1.8252</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2968</v>
+        <v>2.4572</v>
       </c>
       <c r="G4" t="n">
         <v>2.4368</v>
@@ -766,13 +766,13 @@
         <v>3.5253</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.9286</v>
+        <v>-0.8737</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.4674</v>
+        <v>-0.5729</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4612</v>
+        <v>-0.3008</v>
       </c>
       <c r="V4" t="n">
         <v>1.1525</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5865</v>
+        <v>2.8273</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1053</v>
+        <v>3.0789</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5188</v>
+        <v>-0.2515</v>
       </c>
       <c r="G5" t="n">
         <v>4.5757</v>
@@ -844,13 +844,13 @@
         <v>2.546</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5346</v>
+        <v>-0.2938</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0159</v>
+        <v>-0.0106</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5505</v>
+        <v>-0.2832</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0629</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6868</v>
+        <v>0.2313</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0735</v>
+        <v>-0.2617</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7603</v>
+        <v>0.493</v>
       </c>
       <c r="G6" t="n">
         <v>-0.8054</v>
@@ -922,13 +922,13 @@
         <v>1.9585</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2376</v>
+        <v>-0.2179</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2535</v>
+        <v>0.0653</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0159</v>
+        <v>-0.2832</v>
       </c>
       <c r="V6" t="n">
         <v>0.2754</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7411</v>
+        <v>-0.612</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3296</v>
+        <v>0.4319</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0706</v>
+        <v>-1.0439</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0519</v>
@@ -1078,13 +1078,13 @@
         <v>0.1958</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5521</v>
+        <v>-0.423</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.297</v>
+        <v>-0.1947</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2551</v>
+        <v>-0.2283</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3329</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4968</v>
+        <v>-2.5014</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8383</v>
+        <v>-1.7359</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6586</v>
+        <v>-0.7655</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4287</v>
@@ -1156,13 +1156,13 @@
         <v>0.1958</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2848</v>
+        <v>-0.2894</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2376</v>
+        <v>-0.1353</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0472</v>
+        <v>-0.1541</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9054</v>
+        <v>-2.5833</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2762</v>
+        <v>-2.1144</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6293</v>
+        <v>-0.4689</v>
       </c>
       <c r="G10" t="n">
         <v>-2.555</v>
@@ -1234,13 +1234,13 @@
         <v>1.7626</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8964</v>
+        <v>-0.5743</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.594</v>
+        <v>-0.4323</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3024</v>
+        <v>-0.142</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2166</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6972</v>
+        <v>-3.7285</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2844</v>
+        <v>-2.1821</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4127</v>
+        <v>-1.5464</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9975</v>
@@ -1312,13 +1312,13 @@
         <v>0.9792</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6943</v>
+        <v>-0.7256</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6534</v>
+        <v>-0.5511</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0409</v>
+        <v>-0.1745</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0053</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.9838</v>
+        <v>13.8747</v>
       </c>
       <c r="E12" t="n">
-        <v>10.7121</v>
+        <v>11.6032</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2716</v>
+        <v>2.2715</v>
       </c>
       <c r="G12" t="n">
         <v>11.0571</v>
@@ -1390,13 +1390,13 @@
         <v>18.6054</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.4902</v>
+        <v>-4.5992</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.3641</v>
+        <v>-2.4733</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.1262</v>
+        <v>-2.126</v>
       </c>
       <c r="V12" t="n">
         <v>-2.3755</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.9461</v>
+        <v>5.6072</v>
       </c>
       <c r="E13" t="n">
-        <v>3.9004</v>
+        <v>4.7191</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0457</v>
+        <v>0.8881</v>
       </c>
       <c r="G13" t="n">
         <v>3.2802</v>
@@ -1468,13 +1468,13 @@
         <v>0.9792</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2327</v>
+        <v>0.8938</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7369</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9697</v>
+        <v>0.8121</v>
       </c>
       <c r="V13" t="n">
         <v>1.8249</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1924</v>
+        <v>2.4283</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7782</v>
+        <v>1.8806</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4141</v>
+        <v>0.5478</v>
       </c>
       <c r="G14" t="n">
         <v>2.0438</v>
@@ -1546,13 +1546,13 @@
         <v>0.1958</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0473</v>
+        <v>0.1886</v>
       </c>
       <c r="T14" t="n">
-        <v>0.077</v>
+        <v>0.1794</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1244</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7499</v>
+        <v>0.8927</v>
       </c>
       <c r="E15" t="n">
-        <v>2.136</v>
+        <v>1.9313</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3861</v>
+        <v>-1.0386</v>
       </c>
       <c r="G15" t="n">
         <v>-1.8435</v>
@@ -1624,13 +1624,13 @@
         <v>1.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0439</v>
+        <v>1.1867</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8651</v>
+        <v>0.6605</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1787</v>
+        <v>0.5262</v>
       </c>
       <c r="V15" t="n">
         <v>1.5495</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MARTINEZ FERREIRO</t>
+          <t>D. WILLIAM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1548</v>
+        <v>-0.646</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0381</v>
+        <v>1.926</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1167</v>
+        <v>-2.572</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6742</v>
+        <v>-3.0027</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1998</v>
+        <v>0.4171</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8739</v>
+        <v>-3.4197</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7935</v>
+        <v>0.1911</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0612</v>
+        <v>0.141</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7323</v>
+        <v>0.0501</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4677</v>
+        <v>-3.1938</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1385</v>
+        <v>0.276</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6062</v>
+        <v>-3.4698</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3917</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9792</v>
+        <v>-2.3502</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5875</v>
+        <v>1.3709</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.08890000000000001</v>
+        <v>1.2357</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1476</v>
+        <v>0.16</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2365</v>
+        <v>1.0757</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.1003</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.9252</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. WILLIAM</t>
+          <t>J. MARTINEZ FERREIRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2646</v>
+        <v>-1.4323</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4144</v>
+        <v>-0.3451</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.6789</v>
+        <v>-1.0872</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.0027</v>
+        <v>-0.6742</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4171</v>
+        <v>0.1998</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.4197</v>
+        <v>-0.8739</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1911</v>
+        <v>0.7935</v>
       </c>
       <c r="K17" t="n">
-        <v>0.141</v>
+        <v>0.0612</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0501</v>
+        <v>0.7323</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.1938</v>
+        <v>-1.4677</v>
       </c>
       <c r="N17" t="n">
-        <v>0.276</v>
+        <v>0.1385</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.4698</v>
+        <v>-1.6062</v>
       </c>
       <c r="P17" t="n">
+        <v>-0.3917</v>
+      </c>
+      <c r="Q17" t="n">
         <v>-0.9792</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-2.3502</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.3709</v>
+        <v>0.5875</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6171</v>
+        <v>-0.3664</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3517</v>
+        <v>-0.1594</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9688</v>
+        <v>-0.207</v>
       </c>
       <c r="V17" t="n">
-        <v>2.1003</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.9252</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.8249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.1847</v>
+        <v>-2.7947</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5274</v>
+        <v>-2.2204</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6573</v>
+        <v>-0.5743</v>
       </c>
       <c r="G18" t="n">
         <v>-3.3728</v>
@@ -1858,13 +1858,13 @@
         <v>0.7834</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3615</v>
+        <v>0.0285</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3805</v>
+        <v>-0.0735</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0191</v>
+        <v>0.102</v>
       </c>
       <c r="V18" t="n">
         <v>0.9412</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. FALL</t>
+          <t>P. SANJURJO BOTEJARA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.546</v>
+        <v>-3.6483</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6329</v>
+        <v>-3.4616</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9131</v>
+        <v>-0.1867</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7744</v>
+        <v>-3.7643</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9983</v>
+        <v>-2.2842</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.7727</v>
+        <v>-1.4802</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7485000000000001</v>
+        <v>-2.5706</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5868</v>
+        <v>-2.0144</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1617</v>
+        <v>-0.5562</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.5229</v>
+        <v>-1.1938</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4114</v>
+        <v>-0.2698</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.9344</v>
+        <v>-0.924</v>
       </c>
       <c r="P19" t="n">
-        <v>-4.1128</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.2879</v>
+        <v>-0.9792</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1751</v>
+        <v>0.9792</v>
       </c>
       <c r="S19" t="n">
-        <v>4.5568</v>
+        <v>0.116</v>
       </c>
       <c r="T19" t="n">
-        <v>3.2971</v>
+        <v>0.0882</v>
       </c>
       <c r="U19" t="n">
-        <v>1.2597</v>
+        <v>0.0278</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.2154</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3905</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. SANJURJO BOTEJARA</t>
+          <t>K. FALL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.9535</v>
+        <v>-5.8019</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.871</v>
+        <v>-3.7819</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-2.02</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.7643</v>
+        <v>-1.7744</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.2842</v>
+        <v>0.9983</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4802</v>
+        <v>-2.7727</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.5706</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.0144</v>
+        <v>0.5868</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5562</v>
+        <v>0.1617</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1938</v>
+        <v>-2.5229</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2698</v>
+        <v>0.4114</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.924</v>
+        <v>-2.9344</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-4.1128</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9792</v>
+        <v>-5.2879</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9792</v>
+        <v>1.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1892</v>
+        <v>2.3008</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3211</v>
+        <v>1.148</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1319</v>
+        <v>1.1528</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.2154</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.3905</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.7685</v>
+        <v>-6.9065</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4313</v>
+        <v>-2.9196</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.3372</v>
+        <v>-3.9869</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9492</v>
@@ -2092,13 +2092,13 @@
         <v>1.5668</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2732</v>
+        <v>0.5887</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4705</v>
+        <v>0.0412</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1973</v>
+        <v>0.5476</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8249</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-12.9837</v>
+        <v>-12.3015</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2717</v>
+        <v>-2.271599999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-10.7121</v>
+        <v>-10.0298</v>
       </c>
       <c r="G22" t="n">
         <v>-11.0571</v>
@@ -2146,7 +2146,7 @@
         <v>5.531499999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3071999999999996</v>
+        <v>0.3071999999999998</v>
       </c>
       <c r="L22" t="n">
         <v>5.2244</v>
@@ -2170,16 +2170,16 @@
         <v>8.813000000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>5.4904</v>
+        <v>6.172400000000001</v>
       </c>
       <c r="T22" t="n">
         <v>2.1261</v>
       </c>
       <c r="U22" t="n">
-        <v>3.3643</v>
+        <v>4.0465</v>
       </c>
       <c r="V22" t="n">
-        <v>2.3756</v>
+        <v>2.375600000000001</v>
       </c>
       <c r="W22" t="n">
         <v>8.676499999999999</v>
